--- a/output/daily_screen_20260918.xlsx
+++ b/output/daily_screen_20260918.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,24 +662,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13138450</v>
+        <v>6628000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -688,70 +688,70 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12818450</v>
+        <v>6628000</v>
       </c>
       <c r="N2" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02496401671028868</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>291.5</v>
+        <v>268.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>291.5</v>
+        <v>268.5</v>
       </c>
       <c r="R2" t="n">
-        <v>60882971</v>
+        <v>28876533</v>
       </c>
       <c r="S2" t="n">
-        <v>267.3</v>
+        <v>236.9</v>
       </c>
       <c r="T2" t="n">
-        <v>262.6</v>
+        <v>229.125</v>
       </c>
       <c r="U2" t="n">
-        <v>259.625</v>
+        <v>225.85</v>
       </c>
       <c r="V2" t="n">
-        <v>264.8771377563477</v>
+        <v>219.4216664632162</v>
       </c>
       <c r="W2" t="n">
-        <v>4.90951589695112</v>
+        <v>7.157331818098015</v>
       </c>
       <c r="X2" t="n">
-        <v>3.616993575845766</v>
+        <v>4.149254290737223</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.292522321105354</v>
+        <v>3.008077527360792</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.290442307315957</v>
+        <v>-0.06954122606925317</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2564655172413792</v>
+        <v>0.3226600985221675</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.002455046170491415</v>
+        <v>0.2766291981904738</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2132042304846948</v>
+        <v>0.2793988117654831</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.02246332732296497</v>
+        <v>0.2566209170380003</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2356675578076598</v>
+        <v>0.02277789472748282</v>
       </c>
       <c r="AG2" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AH2" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -790,12 +790,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,15 +813,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6628000</v>
+        <v>89118000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6628000</v>
+        <v>89118000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -839,61 +839,61 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>268.5</v>
+        <v>156</v>
       </c>
       <c r="Q3" t="n">
-        <v>268.5</v>
+        <v>156</v>
       </c>
       <c r="R3" t="n">
-        <v>29318025</v>
+        <v>301927693</v>
       </c>
       <c r="S3" t="n">
-        <v>236.9</v>
+        <v>145.3</v>
       </c>
       <c r="T3" t="n">
-        <v>229.125</v>
+        <v>134.7</v>
       </c>
       <c r="U3" t="n">
-        <v>225.85</v>
+        <v>132.725</v>
       </c>
       <c r="V3" t="n">
-        <v>219.4216664632162</v>
+        <v>135.3345667521159</v>
       </c>
       <c r="W3" t="n">
-        <v>7.157331818098015</v>
+        <v>5.85870226863986</v>
       </c>
       <c r="X3" t="n">
-        <v>4.149254290737224</v>
+        <v>4.271703269031681</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.008077527360792</v>
+        <v>1.586998999608179</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.06954122606925406</v>
+        <v>0.8331355950464547</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3226600985221675</v>
+        <v>0.3390557939914163</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2766291981904738</v>
+        <v>-0.03250101068831279</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2793988117654831</v>
+        <v>0.2957945072347319</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2566209170380003</v>
+        <v>-0.05250929184078634</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.02277789472748282</v>
+        <v>0.3483037990755182</v>
       </c>
       <c r="AG3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>94.2</v>
+        <v>91.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>89118000</v>
+        <v>13138450</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>89118000</v>
+        <v>13138450</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -981,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>156</v>
+        <v>291.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>156</v>
+        <v>291.5</v>
       </c>
       <c r="R4" t="n">
-        <v>304492774</v>
+        <v>57571978</v>
       </c>
       <c r="S4" t="n">
-        <v>145.3</v>
+        <v>267.3</v>
       </c>
       <c r="T4" t="n">
-        <v>134.7</v>
+        <v>262.6</v>
       </c>
       <c r="U4" t="n">
-        <v>132.725</v>
+        <v>259.625</v>
       </c>
       <c r="V4" t="n">
-        <v>135.3345667521159</v>
+        <v>264.8771377563477</v>
       </c>
       <c r="W4" t="n">
-        <v>5.85870226863986</v>
+        <v>4.90951589695112</v>
       </c>
       <c r="X4" t="n">
-        <v>4.271703269031672</v>
+        <v>3.616993575845758</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.586998999608188</v>
+        <v>1.292522321105362</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8331355950464654</v>
+        <v>-1.290442307315947</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3390557939914163</v>
+        <v>0.2564655172413792</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.03250101068831279</v>
+        <v>-0.002455046170491415</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2957945072347319</v>
+        <v>0.2132042304846948</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.05250929184078634</v>
+        <v>-0.02246332732296497</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3483037990755182</v>
+        <v>0.2356675578076598</v>
       </c>
       <c r="AG4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>86.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1129,7 +1129,7 @@
         <v>7150</v>
       </c>
       <c r="R5" t="n">
-        <v>2665795</v>
+        <v>2507803</v>
       </c>
       <c r="S5" t="n">
         <v>6451</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1271,7 +1271,7 @@
         <v>638</v>
       </c>
       <c r="R6" t="n">
-        <v>26277732</v>
+        <v>24914833</v>
       </c>
       <c r="S6" t="n">
         <v>612.2</v>
@@ -1289,13 +1289,13 @@
         <v>4.54865328040853</v>
       </c>
       <c r="X6" t="n">
-        <v>3.361785660942133</v>
+        <v>3.361785660942132</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.186867619466397</v>
+        <v>1.186867619466398</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.26328025977577</v>
+        <v>-1.263280259775768</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>84.60000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1413,7 +1413,7 @@
         <v>1430</v>
       </c>
       <c r="R7" t="n">
-        <v>2470296</v>
+        <v>2284855</v>
       </c>
       <c r="S7" t="n">
         <v>1297</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>84.39999999999999</v>
+        <v>85.19999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1555,7 +1555,7 @@
         <v>19290</v>
       </c>
       <c r="R8" t="n">
-        <v>258325</v>
+        <v>226587</v>
       </c>
       <c r="S8" t="n">
         <v>18263</v>
@@ -1573,13 +1573,13 @@
         <v>501.2090599220355</v>
       </c>
       <c r="X8" t="n">
-        <v>498.3696675948676</v>
+        <v>498.3696675948691</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.8393923271679</v>
+        <v>2.839392327166422</v>
       </c>
       <c r="Z8" t="n">
-        <v>-86.09304502013049</v>
+        <v>-86.09304502013237</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1697,7 +1697,7 @@
         <v>2460</v>
       </c>
       <c r="R9" t="n">
-        <v>37087655</v>
+        <v>35352856</v>
       </c>
       <c r="S9" t="n">
         <v>2403.2029296875</v>
@@ -1712,16 +1712,16 @@
         <v>2391.566548665365</v>
       </c>
       <c r="W9" t="n">
-        <v>6.683577550756127</v>
+        <v>6.683577553562827</v>
       </c>
       <c r="X9" t="n">
-        <v>5.805527534525496</v>
+        <v>5.805527540120512</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8780500162306311</v>
+        <v>0.8780500134423157</v>
       </c>
       <c r="Z9" t="n">
-        <v>-4.850089968250263</v>
+        <v>-4.850089971385047</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1839,7 +1839,7 @@
         <v>168.5</v>
       </c>
       <c r="R10" t="n">
-        <v>39800574</v>
+        <v>39566848</v>
       </c>
       <c r="S10" t="n">
         <v>162.5</v>
@@ -1857,13 +1857,13 @@
         <v>4.841302244193912</v>
       </c>
       <c r="X10" t="n">
-        <v>3.603842163751634</v>
+        <v>3.603842163751633</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.237460080442278</v>
+        <v>1.237460080442279</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.882380615828207</v>
+        <v>0.8823806158282088</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>78.2</v>
+        <v>79</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1981,7 +1981,7 @@
         <v>2290</v>
       </c>
       <c r="R11" t="n">
-        <v>2561193</v>
+        <v>2467978</v>
       </c>
       <c r="S11" t="n">
         <v>2137</v>
@@ -2002,10 +2002,10 @@
         <v>17.73224598950311</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.019440368839227</v>
+        <v>6.019440368839231</v>
       </c>
       <c r="Z11" t="n">
-        <v>-10.7947947427672</v>
+        <v>-10.79479474276719</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2123,7 +2123,7 @@
         <v>94</v>
       </c>
       <c r="R12" t="n">
-        <v>41307139</v>
+        <v>40838185</v>
       </c>
       <c r="S12" t="n">
         <v>87.75999908447265</v>
@@ -2141,13 +2141,13 @@
         <v>-0.1445699702847065</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4191349979368822</v>
+        <v>-0.4191349979368845</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2745650276521757</v>
+        <v>0.274565027652178</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.4784430208420858</v>
+        <v>-0.478443020842083</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>73.39999999999999</v>
+        <v>74.19999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2265,7 +2265,7 @@
         <v>172</v>
       </c>
       <c r="R13" t="n">
-        <v>32376510</v>
+        <v>32080817</v>
       </c>
       <c r="S13" t="n">
         <v>161.6</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2407,7 +2407,7 @@
         <v>343</v>
       </c>
       <c r="R14" t="n">
-        <v>21472344</v>
+        <v>21255470</v>
       </c>
       <c r="S14" t="n">
         <v>338.6</v>
@@ -2425,13 +2425,13 @@
         <v>2.63249156037142</v>
       </c>
       <c r="X14" t="n">
-        <v>2.594405376900291</v>
+        <v>2.594405376900235</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03808618347112969</v>
+        <v>0.03808618347118564</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.2171913959405547</v>
+        <v>-0.2171913959404845</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2517,15 +2517,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2546000</v>
+        <v>1000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2546000</v>
+        <v>1000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2543,61 +2543,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5800</v>
+        <v>568</v>
       </c>
       <c r="Q15" t="n">
-        <v>5800</v>
+        <v>568</v>
       </c>
       <c r="R15" t="n">
-        <v>819542</v>
+        <v>790739</v>
       </c>
       <c r="S15" t="n">
-        <v>5587</v>
+        <v>545</v>
       </c>
       <c r="T15" t="n">
-        <v>5421.5</v>
+        <v>559.15</v>
       </c>
       <c r="U15" t="n">
-        <v>5404.75</v>
+        <v>559.05</v>
       </c>
       <c r="V15" t="n">
-        <v>5859.152449544271</v>
+        <v>583.5542490641276</v>
       </c>
       <c r="W15" t="n">
-        <v>40.07770455340778</v>
+        <v>-4.520297081422996</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.399118806738633</v>
+        <v>-7.327279189040619</v>
       </c>
       <c r="Y15" t="n">
-        <v>49.47682336014642</v>
+        <v>2.806982107617623</v>
       </c>
       <c r="Z15" t="n">
-        <v>32.49559175977198</v>
+        <v>0.06981058845947175</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.06129917657822515</v>
+        <v>0.003533568904593665</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1046431035983798</v>
+        <v>-0.05131173484512697</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01803788982154075</v>
+        <v>-0.03972771785209073</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1246513847508534</v>
+        <v>-0.07132001599760052</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1426892745723941</v>
+        <v>0.03159229814550979</v>
       </c>
       <c r="AG15" t="n">
-        <v>57.99999999999999</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,15 +2659,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>3988000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>3988000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2685,61 +2685,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>568</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="Q16" t="n">
-        <v>568</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="R16" t="n">
-        <v>823895</v>
+        <v>926007</v>
       </c>
       <c r="S16" t="n">
-        <v>545</v>
+        <v>82.21999816894531</v>
       </c>
       <c r="T16" t="n">
-        <v>559.15</v>
+        <v>82.51499938964844</v>
       </c>
       <c r="U16" t="n">
-        <v>559.05</v>
+        <v>82.45499954223632</v>
       </c>
       <c r="V16" t="n">
-        <v>583.5542490641276</v>
+        <v>88.16086870829264</v>
       </c>
       <c r="W16" t="n">
-        <v>-4.520297081422996</v>
+        <v>-0.2671380369940124</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.327279189040595</v>
+        <v>-0.4930699499440507</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.8069821076176</v>
+        <v>0.2259319129500383</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.06981058845944332</v>
+        <v>0.1261968535915994</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.003533568904593665</v>
+        <v>0.0146341091249047</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.05131173484512697</v>
+        <v>-0.1512215814011411</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.03972771785209073</v>
+        <v>-0.02862717763177969</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.07132001599760052</v>
+        <v>-0.1712298625536146</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03159229814550979</v>
+        <v>0.1426026849218349</v>
       </c>
       <c r="AG16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AH16" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2792,24 +2792,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3988000</v>
+        <v>2544000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2818,70 +2818,70 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3988000</v>
+        <v>2546000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.0007855459544383347</v>
       </c>
       <c r="P17" t="n">
-        <v>83.19999694824219</v>
+        <v>5800</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.19999694824219</v>
+        <v>5800</v>
       </c>
       <c r="R17" t="n">
-        <v>936837</v>
+        <v>743553</v>
       </c>
       <c r="S17" t="n">
-        <v>82.21999816894531</v>
+        <v>5587</v>
       </c>
       <c r="T17" t="n">
-        <v>82.51499938964844</v>
+        <v>5421.5</v>
       </c>
       <c r="U17" t="n">
-        <v>82.45499954223632</v>
+        <v>5404.75</v>
       </c>
       <c r="V17" t="n">
-        <v>88.16086870829264</v>
+        <v>5859.152449544271</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2671380369940124</v>
+        <v>40.07770455340778</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4930699499440415</v>
+        <v>-9.399118806739123</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2259319129500291</v>
+        <v>49.47682336014691</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1261968535915878</v>
+        <v>32.49559175977259</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0146341091249047</v>
+        <v>0.06129917657822515</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1512215814011411</v>
+        <v>-0.1046431035983798</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.02862717763177969</v>
+        <v>0.01803788982154075</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.1712298625536146</v>
+        <v>-0.1246513847508534</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1426026849218349</v>
+        <v>0.1426892745723941</v>
       </c>
       <c r="AG17" t="n">
-        <v>40</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH17" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65.8</v>
+        <v>57.39999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2960,13 +2960,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1731000</v>
+        <v>1773000</v>
       </c>
       <c r="N18" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02426343154246101</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>2295</v>
@@ -2975,7 +2975,7 @@
         <v>2295</v>
       </c>
       <c r="R18" t="n">
-        <v>1513886</v>
+        <v>1430448</v>
       </c>
       <c r="S18" t="n">
         <v>2124</v>
@@ -2993,13 +2993,13 @@
         <v>40.19777325642099</v>
       </c>
       <c r="X18" t="n">
-        <v>61.2215812731859</v>
+        <v>61.22158127318583</v>
       </c>
       <c r="Y18" t="n">
-        <v>-21.02380801676491</v>
+        <v>-21.02380801676484</v>
       </c>
       <c r="Z18" t="n">
-        <v>-43.73238480091425</v>
+        <v>-43.73238480091416</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>56.4</v>
+        <v>57.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3115,7 +3115,7 @@
         <v>3520</v>
       </c>
       <c r="R19" t="n">
-        <v>481719</v>
+        <v>450137</v>
       </c>
       <c r="S19" t="n">
         <v>3316</v>
@@ -3130,16 +3130,16 @@
         <v>2916.045678710937</v>
       </c>
       <c r="W19" t="n">
-        <v>92.58585385772358</v>
+        <v>92.58585385772449</v>
       </c>
       <c r="X19" t="n">
-        <v>128.3061201234458</v>
+        <v>128.3061201234465</v>
       </c>
       <c r="Y19" t="n">
-        <v>-35.72026626572224</v>
+        <v>-35.72026626572199</v>
       </c>
       <c r="Z19" t="n">
-        <v>-58.27059034016247</v>
+        <v>-58.27059034016261</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53.6</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>3430</v>
       </c>
       <c r="R20" t="n">
-        <v>3710579</v>
+        <v>3510469</v>
       </c>
       <c r="S20" t="n">
         <v>3243</v>
@@ -3273,13 +3273,13 @@
         <v>34.24072461730566</v>
       </c>
       <c r="X20" t="n">
-        <v>68.38340982289499</v>
+        <v>68.38340982289496</v>
       </c>
       <c r="Y20" t="n">
-        <v>-34.14268520558933</v>
+        <v>-34.1426852055893</v>
       </c>
       <c r="Z20" t="n">
-        <v>-60.21748888459419</v>
+        <v>-60.21748888459415</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>52.59999999999999</v>
+        <v>53.39999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3395,7 +3395,7 @@
         <v>4710</v>
       </c>
       <c r="R21" t="n">
-        <v>9902031</v>
+        <v>9019674</v>
       </c>
       <c r="S21" t="n">
         <v>4546</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45.8</v>
+        <v>46.59999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3535,7 +3535,7 @@
         <v>229.5</v>
       </c>
       <c r="R22" t="n">
-        <v>3288686</v>
+        <v>3236175</v>
       </c>
       <c r="S22" t="n">
         <v>224.7</v>
@@ -3553,13 +3553,13 @@
         <v>4.324383270149951</v>
       </c>
       <c r="X22" t="n">
-        <v>5.164658162088113</v>
+        <v>5.164658162088111</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.8402748919381615</v>
+        <v>-0.8402748919381597</v>
       </c>
       <c r="Z22" t="n">
-        <v>-1.221708814993867</v>
+        <v>-1.221708814993865</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>45.2</v>
+        <v>46</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3675,7 +3675,7 @@
         <v>611</v>
       </c>
       <c r="R23" t="n">
-        <v>10006571</v>
+        <v>9566954</v>
       </c>
       <c r="S23" t="n">
         <v>554</v>
@@ -3693,13 +3693,13 @@
         <v>0.08787589625183045</v>
       </c>
       <c r="X23" t="n">
-        <v>3.415872853763298</v>
+        <v>3.415872853763296</v>
       </c>
       <c r="Y23" t="n">
-        <v>-3.327996957511467</v>
+        <v>-3.327996957511466</v>
       </c>
       <c r="Z23" t="n">
-        <v>-10.98015130813657</v>
+        <v>-10.98015130813656</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>44.2</v>
+        <v>45</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3815,7 +3815,7 @@
         <v>499.5</v>
       </c>
       <c r="R24" t="n">
-        <v>4517729</v>
+        <v>4292625</v>
       </c>
       <c r="S24" t="n">
         <v>497.6</v>
@@ -3830,16 +3830,16 @@
         <v>451.4860285441081</v>
       </c>
       <c r="W24" t="n">
-        <v>7.50141690379121</v>
+        <v>7.501416903791153</v>
       </c>
       <c r="X24" t="n">
-        <v>14.75768191543658</v>
+        <v>14.7576819154365</v>
       </c>
       <c r="Y24" t="n">
-        <v>-7.25626501164537</v>
+        <v>-7.256265011645343</v>
       </c>
       <c r="Z24" t="n">
-        <v>-8.316435980138333</v>
+        <v>-8.316435980138301</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>42.40000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3955,7 +3955,7 @@
         <v>196</v>
       </c>
       <c r="R25" t="n">
-        <v>3899723</v>
+        <v>3831061</v>
       </c>
       <c r="S25" t="n">
         <v>185.8</v>
@@ -3973,13 +3973,13 @@
         <v>0.3198034157382779</v>
       </c>
       <c r="X25" t="n">
-        <v>1.54174508841428</v>
+        <v>1.541745088414272</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.221941672676002</v>
+        <v>-1.221941672675994</v>
       </c>
       <c r="Z25" t="n">
-        <v>-2.689292851735097</v>
+        <v>-2.689292851735087</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>38.8</v>
+        <v>39.60000000000001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4095,7 +4095,7 @@
         <v>102</v>
       </c>
       <c r="R26" t="n">
-        <v>2100526</v>
+        <v>2085504</v>
       </c>
       <c r="S26" t="n">
         <v>100.8800003051758</v>
@@ -4113,13 +4113,13 @@
         <v>2.066400656835398</v>
       </c>
       <c r="X26" t="n">
-        <v>2.24761560500442</v>
+        <v>2.247615605004416</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.1812149481690222</v>
+        <v>-0.1812149481690177</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.187520899788967</v>
+        <v>-0.1875208997889617</v>
       </c>
       <c r="AA26" t="b">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>38.8</v>
+        <v>39.6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4233,7 +4233,7 @@
         <v>250.5</v>
       </c>
       <c r="R27" t="n">
-        <v>44422531</v>
+        <v>43948586</v>
       </c>
       <c r="S27" t="n">
         <v>248.8</v>
@@ -4251,13 +4251,13 @@
         <v>-0.5114268311859291</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.4261924078338075</v>
+        <v>-0.4261924078338091</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.08523442335212161</v>
+        <v>-0.08523442335212</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.291258863486621</v>
+        <v>-0.291258863486619</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>35.8</v>
+        <v>36.59999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4373,7 +4373,7 @@
         <v>525</v>
       </c>
       <c r="R28" t="n">
-        <v>79318936</v>
+        <v>76407003</v>
       </c>
       <c r="S28" t="n">
         <v>488.8</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4511,7 +4511,7 @@
         <v>2210</v>
       </c>
       <c r="R29" t="n">
-        <v>6443131</v>
+        <v>5964833</v>
       </c>
       <c r="S29" t="n">
         <v>2030</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>41.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4651,7 +4651,7 @@
         <v>6430</v>
       </c>
       <c r="R30" t="n">
-        <v>2808375</v>
+        <v>2691196</v>
       </c>
       <c r="S30" t="n">
         <v>6145</v>
@@ -4669,13 +4669,13 @@
         <v>-1.35643354784861</v>
       </c>
       <c r="X30" t="n">
-        <v>173.6438704748119</v>
+        <v>173.6438704748116</v>
       </c>
       <c r="Y30" t="n">
-        <v>-175.0003040226605</v>
+        <v>-175.0003040226602</v>
       </c>
       <c r="Z30" t="n">
-        <v>-229.6430961567775</v>
+        <v>-229.6430961567771</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4748,24 +4748,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37.6</v>
+        <v>35.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1234000</v>
+        <v>501000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>219000</v>
+        <v>501000</v>
       </c>
       <c r="N31" t="n">
-        <v>1015000</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.634703196347032</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1020</v>
+        <v>228.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1020</v>
+        <v>228.5</v>
       </c>
       <c r="R31" t="n">
-        <v>11121177</v>
+        <v>25619855</v>
       </c>
       <c r="S31" t="n">
-        <v>990.8</v>
+        <v>222.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1057.65</v>
+        <v>231.475</v>
       </c>
       <c r="U31" t="n">
-        <v>1054.9</v>
+        <v>230.725</v>
       </c>
       <c r="V31" t="n">
-        <v>1021.366666666667</v>
+        <v>218.375</v>
       </c>
       <c r="W31" t="n">
-        <v>-17.91455955000981</v>
+        <v>-1.247059460996297</v>
       </c>
       <c r="X31" t="n">
-        <v>-1.791765994811171</v>
+        <v>0.8791686726365886</v>
       </c>
       <c r="Y31" t="n">
-        <v>-16.12279355519864</v>
+        <v>-2.126228133632886</v>
       </c>
       <c r="Z31" t="n">
-        <v>-23.31903874399093</v>
+        <v>-3.319347823319499</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.05699481865284972</v>
+        <v>0.07025761124121788</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1428571428571429</v>
+        <v>0.02696629213483148</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.01373353189616533</v>
+        <v>0.02699632448453348</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.1628654240096165</v>
+        <v>0.006958010982357932</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1765989559057818</v>
+        <v>0.02003831350217555</v>
       </c>
       <c r="AG31" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         <v>1</v>
       </c>
       <c r="AN31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>1201.56</v>
+        <v>252.72</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>34.59999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4897,15 +4897,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>501000</v>
+        <v>2512000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>501000</v>
+        <v>2512000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4923,61 +4923,61 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>228.5</v>
+        <v>5525</v>
       </c>
       <c r="Q32" t="n">
-        <v>228.5</v>
+        <v>5525</v>
       </c>
       <c r="R32" t="n">
-        <v>25747122</v>
+        <v>1008538</v>
       </c>
       <c r="S32" t="n">
-        <v>222.3</v>
+        <v>5450</v>
       </c>
       <c r="T32" t="n">
-        <v>231.475</v>
+        <v>5621</v>
       </c>
       <c r="U32" t="n">
-        <v>230.725</v>
+        <v>5614.5</v>
       </c>
       <c r="V32" t="n">
-        <v>218.375</v>
+        <v>4428.819962565104</v>
       </c>
       <c r="W32" t="n">
-        <v>-1.247059460996297</v>
+        <v>20.61735946063436</v>
       </c>
       <c r="X32" t="n">
-        <v>0.8791686726365886</v>
+        <v>123.7119118084013</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.126228133632886</v>
+        <v>-103.0945523477669</v>
       </c>
       <c r="Z32" t="n">
-        <v>-3.319347823319499</v>
+        <v>-127.9880141951272</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.07025761124121788</v>
+        <v>0.02409638554216875</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.02696629213483148</v>
+        <v>0.6326885157363356</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.02699632448453348</v>
+        <v>-0.01916490121451564</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.006958010982357932</v>
+        <v>0.612680234583862</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.02003831350217555</v>
+        <v>-0.6318451357983776</v>
       </c>
       <c r="AG32" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="AH32" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4995,11 +4995,9 @@
         <v>1</v>
       </c>
       <c r="AN32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>252.72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5014,12 +5012,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5028,7 +5026,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>34.4</v>
+        <v>33.40000000000001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5037,15 +5035,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2512000</v>
+        <v>1000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5054,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2512000</v>
+        <v>1000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5063,61 +5061,61 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>5525</v>
+        <v>1250</v>
       </c>
       <c r="Q33" t="n">
-        <v>5525</v>
+        <v>1250</v>
       </c>
       <c r="R33" t="n">
-        <v>1045790</v>
+        <v>995532</v>
       </c>
       <c r="S33" t="n">
-        <v>5450</v>
+        <v>1224</v>
       </c>
       <c r="T33" t="n">
-        <v>5621</v>
+        <v>1298.5</v>
       </c>
       <c r="U33" t="n">
-        <v>5614.5</v>
+        <v>1295.75</v>
       </c>
       <c r="V33" t="n">
-        <v>4428.819962565104</v>
+        <v>1138.089337158203</v>
       </c>
       <c r="W33" t="n">
-        <v>20.61735946063436</v>
+        <v>-14.00170947505671</v>
       </c>
       <c r="X33" t="n">
-        <v>123.7119118084014</v>
+        <v>4.868739271976048</v>
       </c>
       <c r="Y33" t="n">
-        <v>-103.094552347767</v>
+        <v>-18.87044874703276</v>
       </c>
       <c r="Z33" t="n">
-        <v>-127.9880141951273</v>
+        <v>-25.27951942064689</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.02409638554216875</v>
+        <v>0.04602510460251041</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.6326885157363356</v>
+        <v>0.1775713143627822</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01916490121451564</v>
+        <v>0.002763817845826022</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.612680234583862</v>
+        <v>0.1575630332103086</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.6318451357983776</v>
+        <v>-0.1547992153644826</v>
       </c>
       <c r="AG33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AH33" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5137,7 +5135,9 @@
       <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>1462.5</v>
+      </c>
       <c r="AP33" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5175,24 +5175,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1000</v>
+        <v>7240000</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1000</v>
+        <v>7240000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5201,67 +5201,67 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1250</v>
+        <v>1735</v>
       </c>
       <c r="Q34" t="n">
-        <v>1250</v>
+        <v>1735</v>
       </c>
       <c r="R34" t="n">
-        <v>1017579</v>
+        <v>12081302</v>
       </c>
       <c r="S34" t="n">
-        <v>1224</v>
+        <v>1684</v>
       </c>
       <c r="T34" t="n">
-        <v>1298.5</v>
+        <v>1749</v>
       </c>
       <c r="U34" t="n">
-        <v>1295.75</v>
+        <v>1749.75</v>
       </c>
       <c r="V34" t="n">
-        <v>1138.089337158203</v>
+        <v>1784.833333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>-14.00170947505671</v>
+        <v>-21.55731083348405</v>
       </c>
       <c r="X34" t="n">
-        <v>4.868739271976094</v>
+        <v>-18.67907128338327</v>
       </c>
       <c r="Y34" t="n">
-        <v>-18.87044874703281</v>
+        <v>-2.87823955010078</v>
       </c>
       <c r="Z34" t="n">
-        <v>-25.27951942064695</v>
+        <v>-10.58539700714683</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.04602510460251041</v>
+        <v>-0.008571428571428563</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.1775713143627822</v>
+        <v>-0.04143646408839774</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.002763817845826022</v>
+        <v>-0.05183271532811295</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.1575630332103086</v>
+        <v>-0.06144474524087129</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.1547992153644826</v>
+        <v>0.009612029912758335</v>
       </c>
       <c r="AG34" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AH34" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
       </c>
       <c r="AJ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="b">
         <v>0</v>
@@ -5273,15 +5273,13 @@
         <v>1</v>
       </c>
       <c r="AN34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" t="n">
-        <v>1462.5</v>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>1769.7</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1749.74</v>
       </c>
     </row>
     <row r="35">
@@ -5292,12 +5290,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5315,24 +5313,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7240000</v>
+        <v>2712000</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>7240000</v>
+        <v>2712000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5341,67 +5339,67 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1735</v>
+        <v>473</v>
       </c>
       <c r="Q35" t="n">
-        <v>1735</v>
+        <v>473</v>
       </c>
       <c r="R35" t="n">
-        <v>12673351</v>
+        <v>28806674</v>
       </c>
       <c r="S35" t="n">
-        <v>1684</v>
+        <v>481.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1749</v>
+        <v>483.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1749.75</v>
+        <v>481.7</v>
       </c>
       <c r="V35" t="n">
-        <v>1784.833333333333</v>
+        <v>503.5833333333333</v>
       </c>
       <c r="W35" t="n">
-        <v>-21.55731083348405</v>
+        <v>-0.6202561138278497</v>
       </c>
       <c r="X35" t="n">
-        <v>-18.67907128338327</v>
+        <v>2.564723127082567</v>
       </c>
       <c r="Y35" t="n">
-        <v>-2.878239550100783</v>
+        <v>-3.184979240910416</v>
       </c>
       <c r="Z35" t="n">
-        <v>-10.58539700714684</v>
+        <v>-2.320708026354942</v>
       </c>
       <c r="AA35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.008571428571428563</v>
+        <v>0.07256235827664392</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.04143646408839774</v>
+        <v>-0.1844827586206896</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.05183271532811295</v>
+        <v>0.02930107151995953</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.06144474524087129</v>
+        <v>-0.2044910397731632</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.009612029912758335</v>
+        <v>0.2337921112931227</v>
       </c>
       <c r="AG35" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="AH35" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
       </c>
       <c r="AJ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="b">
         <v>0</v>
@@ -5410,16 +5408,18 @@
         <v>0</v>
       </c>
       <c r="AM35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="b">
         <v>1</v>
       </c>
       <c r="AO35" t="n">
-        <v>1769.7</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1749.74</v>
+        <v>508.95</v>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>30.2</v>
+        <v>28.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5453,24 +5453,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2712000</v>
+        <v>24987000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2712000</v>
+        <v>24987000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5479,87 +5479,87 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>473</v>
+        <v>550</v>
       </c>
       <c r="Q36" t="n">
-        <v>473</v>
+        <v>550</v>
       </c>
       <c r="R36" t="n">
-        <v>29733954</v>
+        <v>25526267</v>
       </c>
       <c r="S36" t="n">
-        <v>481.9</v>
+        <v>539.4</v>
       </c>
       <c r="T36" t="n">
-        <v>483.3</v>
+        <v>552.2</v>
       </c>
       <c r="U36" t="n">
-        <v>481.7</v>
+        <v>552.4</v>
       </c>
       <c r="V36" t="n">
-        <v>503.5833333333333</v>
+        <v>661.4083333333333</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.6202561138278497</v>
+        <v>-8.230428016433621</v>
       </c>
       <c r="X36" t="n">
-        <v>2.564723127082567</v>
+        <v>-8.65843188349889</v>
       </c>
       <c r="Y36" t="n">
-        <v>-3.184979240910417</v>
+        <v>0.4280038670652697</v>
       </c>
       <c r="Z36" t="n">
-        <v>-2.320708026354943</v>
+        <v>-1.218632180882587</v>
       </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.07256235827664392</v>
+        <v>-0.007220216606498187</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.1844827586206896</v>
+        <v>-0.458128078817734</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.02930107151995953</v>
+        <v>-0.05048150336318258</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.2044910397731632</v>
+        <v>-0.4781363599702075</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2337921112931227</v>
+        <v>0.427654856607025</v>
       </c>
       <c r="AG36" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="AH36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>508.95</v>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP36" t="n">
+        <v>553.3200000000001</v>
       </c>
     </row>
     <row r="37">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5593,24 +5593,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9426000</v>
+        <v>1234000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>9426000</v>
+        <v>1234000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5619,73 +5619,73 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="Q37" t="n">
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="R37" t="n">
-        <v>10156130</v>
+        <v>10826832</v>
       </c>
       <c r="S37" t="n">
-        <v>1082</v>
+        <v>990.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1127.25</v>
+        <v>1057.65</v>
       </c>
       <c r="U37" t="n">
-        <v>1129</v>
+        <v>1054.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1139</v>
+        <v>1021.366666666667</v>
       </c>
       <c r="W37" t="n">
-        <v>-17.74030052988269</v>
+        <v>-17.91455955000981</v>
       </c>
       <c r="X37" t="n">
-        <v>-19.86038036342022</v>
+        <v>-1.791765994811183</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.120079833537535</v>
+        <v>-16.12279355519863</v>
       </c>
       <c r="Z37" t="n">
-        <v>-1.480635292806117</v>
+        <v>-23.31903874399091</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.03083700440528636</v>
+        <v>0.05699481865284972</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.02222222222222225</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.07409829116197075</v>
+        <v>0.01373353189616533</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.0422305033746958</v>
+        <v>-0.1628654240096165</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.03186778778727495</v>
+        <v>0.1765989559057818</v>
       </c>
       <c r="AG37" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="AH37" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="b">
         <v>1</v>
@@ -5693,13 +5693,13 @@
       <c r="AN37" t="b">
         <v>0</v>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP37" t="n">
-        <v>1163.68</v>
+      <c r="AO37" t="n">
+        <v>1201.56</v>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5733,15 +5733,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>24987000</v>
+        <v>20300000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>24987000</v>
+        <v>20300000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5759,61 +5759,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>550</v>
+        <v>981</v>
       </c>
       <c r="Q38" t="n">
-        <v>550</v>
+        <v>981</v>
       </c>
       <c r="R38" t="n">
-        <v>26151583</v>
+        <v>13722988</v>
       </c>
       <c r="S38" t="n">
-        <v>539.4</v>
+        <v>960.6</v>
       </c>
       <c r="T38" t="n">
-        <v>552.2</v>
+        <v>1002.9</v>
       </c>
       <c r="U38" t="n">
-        <v>552.4</v>
+        <v>1008.1</v>
       </c>
       <c r="V38" t="n">
-        <v>661.4083333333333</v>
+        <v>952.8452178955079</v>
       </c>
       <c r="W38" t="n">
-        <v>-8.230428016433621</v>
+        <v>-13.45221730330491</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.658431883498887</v>
+        <v>-12.96256747875982</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.4280038670652662</v>
+        <v>-0.4896498245450864</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.21863218088259</v>
+        <v>-4.49436641753198</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.007220216606498187</v>
+        <v>-0.09585253456221199</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.458128078817734</v>
+        <v>0.008214088321632396</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.05048150336318258</v>
+        <v>-0.1391138213188964</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.4781363599702075</v>
+        <v>-0.01179419283084115</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.427654856607025</v>
+        <v>-0.1273196284880552</v>
       </c>
       <c r="AG38" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AH38" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5822,24 +5822,22 @@
         <v>0</v>
       </c>
       <c r="AK38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="b">
         <v>1</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>986.89</v>
       </c>
       <c r="AP38" t="n">
-        <v>553.3200000000001</v>
+        <v>1098.05</v>
       </c>
     </row>
     <row r="39">
@@ -5850,12 +5848,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5864,7 +5862,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5873,24 +5871,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>20300000</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>20300000</v>
+        <v>1000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5899,85 +5897,89 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>981</v>
+        <v>944</v>
       </c>
       <c r="Q39" t="n">
-        <v>981</v>
+        <v>944</v>
       </c>
       <c r="R39" t="n">
-        <v>14413731</v>
+        <v>15371023</v>
       </c>
       <c r="S39" t="n">
-        <v>960.6</v>
+        <v>921.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1002.9</v>
+        <v>947.85</v>
       </c>
       <c r="U39" t="n">
-        <v>1008.1</v>
+        <v>947.7</v>
       </c>
       <c r="V39" t="n">
-        <v>952.8452178955079</v>
+        <v>1040.361715698242</v>
       </c>
       <c r="W39" t="n">
-        <v>-13.45221730330491</v>
+        <v>-10.50465947284795</v>
       </c>
       <c r="X39" t="n">
-        <v>-12.96256747875982</v>
+        <v>-11.80607739887391</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.4896498245450882</v>
+        <v>1.301417926025962</v>
       </c>
       <c r="Z39" t="n">
-        <v>-4.494366417531984</v>
+        <v>-1.980802628388833</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.09585253456221199</v>
+        <v>0.003188097768331621</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.008214088321632396</v>
+        <v>0.01244628793164226</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1391138213188964</v>
+        <v>-0.04007318898835277</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.01179419283084115</v>
+        <v>-0.007561993220831287</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.1273196284880552</v>
+        <v>-0.03251119576752148</v>
       </c>
       <c r="AG39" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AH39" t="n">
-        <v>54</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="b">
         <v>1</v>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>986.89</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1098.05</v>
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5988,12 +5990,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6002,24 +6004,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1000</v>
+        <v>5546000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6028,76 +6030,76 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1000</v>
+        <v>5398000</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>148000</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.02741756206002223</v>
       </c>
       <c r="P40" t="n">
-        <v>944</v>
+        <v>1370</v>
       </c>
       <c r="Q40" t="n">
-        <v>944</v>
+        <v>1370</v>
       </c>
       <c r="R40" t="n">
-        <v>15847436</v>
+        <v>9259785</v>
       </c>
       <c r="S40" t="n">
-        <v>921.4</v>
+        <v>1377</v>
       </c>
       <c r="T40" t="n">
-        <v>947.85</v>
+        <v>1405.75</v>
       </c>
       <c r="U40" t="n">
-        <v>947.7</v>
+        <v>1412</v>
       </c>
       <c r="V40" t="n">
-        <v>1040.361715698242</v>
+        <v>1430.583333333333</v>
       </c>
       <c r="W40" t="n">
-        <v>-10.50465947284783</v>
+        <v>-19.92599234664908</v>
       </c>
       <c r="X40" t="n">
-        <v>-11.80607739887374</v>
+        <v>-20.167640543832</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.301417926025909</v>
+        <v>0.2416481971829185</v>
       </c>
       <c r="Z40" t="n">
-        <v>-1.980802628388902</v>
+        <v>-1.561773602172792</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.003188097768331621</v>
+        <v>-0.08361204013377932</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.01244628793164226</v>
+        <v>-0.1329113924050633</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.04007318898835277</v>
+        <v>-0.1268733268904637</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.007561993220831287</v>
+        <v>-0.1529196735575369</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.03251119576752148</v>
+        <v>0.02604634666707317</v>
       </c>
       <c r="AG40" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AH40" t="n">
-        <v>56.00000000000001</v>
+        <v>16</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="b">
         <v>1</v>
@@ -6116,10 +6118,8 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP40" t="n">
+        <v>1492.63</v>
       </c>
     </row>
     <row r="41">
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6185,7 +6185,7 @@
         <v>1855</v>
       </c>
       <c r="R41" t="n">
-        <v>5824801</v>
+        <v>5621672</v>
       </c>
       <c r="S41" t="n">
         <v>1842</v>
@@ -6203,13 +6203,13 @@
         <v>-76.36644509874714</v>
       </c>
       <c r="X41" t="n">
-        <v>-62.46110935546267</v>
+        <v>-62.46110935546268</v>
       </c>
       <c r="Y41" t="n">
-        <v>-13.90533574328446</v>
+        <v>-13.90533574328445</v>
       </c>
       <c r="Z41" t="n">
-        <v>-21.8923560943823</v>
+        <v>-21.89235609438229</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6291,15 +6291,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5972561</v>
+        <v>5656561</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6308,13 +6308,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6332561</v>
+        <v>5972561</v>
       </c>
       <c r="N42" t="n">
-        <v>-360000</v>
+        <v>-316000</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.05684903785372142</v>
+        <v>-0.05290862663437008</v>
       </c>
       <c r="P42" t="n">
         <v>2140</v>
@@ -6323,7 +6323,7 @@
         <v>2140</v>
       </c>
       <c r="R42" t="n">
-        <v>4248107</v>
+        <v>3936746</v>
       </c>
       <c r="S42" t="n">
         <v>2205</v>
@@ -6341,13 +6341,13 @@
         <v>-32.50102851928614</v>
       </c>
       <c r="X42" t="n">
-        <v>22.22598285444398</v>
+        <v>22.22598285444369</v>
       </c>
       <c r="Y42" t="n">
-        <v>-54.72701137373012</v>
+        <v>-54.72701137372982</v>
       </c>
       <c r="Z42" t="n">
-        <v>-56.63304740793645</v>
+        <v>-56.63304740793608</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6461,7 +6461,7 @@
         <v>6435</v>
       </c>
       <c r="R43" t="n">
-        <v>417753</v>
+        <v>390164</v>
       </c>
       <c r="S43" t="n">
         <v>6335</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6599,7 +6599,7 @@
         <v>78.19999694824219</v>
       </c>
       <c r="R44" t="n">
-        <v>1032638</v>
+        <v>1020179</v>
       </c>
       <c r="S44" t="n">
         <v>77.88000030517578</v>
@@ -6617,13 +6617,13 @@
         <v>0.1691209063025383</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.09211058242719503</v>
+        <v>-0.09211058242720732</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.2612314887297333</v>
+        <v>0.2612314887297456</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.2730037064359315</v>
+        <v>0.2730037064359469</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6739,7 +6739,7 @@
         <v>179</v>
       </c>
       <c r="R45" t="n">
-        <v>2484813</v>
+        <v>2446811</v>
       </c>
       <c r="S45" t="n">
         <v>177</v>
@@ -6754,16 +6754,16 @@
         <v>189.1351603190104</v>
       </c>
       <c r="W45" t="n">
-        <v>-5.903432483795655</v>
+        <v>-5.903432483795683</v>
       </c>
       <c r="X45" t="n">
-        <v>-2.360449861354156</v>
+        <v>-2.360449861354219</v>
       </c>
       <c r="Y45" t="n">
-        <v>-3.542982622441498</v>
+        <v>-3.542982622441464</v>
       </c>
       <c r="Z45" t="n">
-        <v>-4.52754738361339</v>
+        <v>-4.527547383613348</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6834,96 +6834,96 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5163000</v>
+        <v>9037000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5163000</v>
+        <v>9426000</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-389000</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>-0.04126883089327393</v>
       </c>
       <c r="P46" t="n">
-        <v>18.75</v>
+        <v>1100</v>
       </c>
       <c r="Q46" t="n">
-        <v>18.75</v>
+        <v>1100</v>
       </c>
       <c r="R46" t="n">
-        <v>25223586</v>
+        <v>9955173</v>
       </c>
       <c r="S46" t="n">
-        <v>18.70999984741211</v>
+        <v>1082</v>
       </c>
       <c r="T46" t="n">
-        <v>18.99249992370606</v>
+        <v>1127.25</v>
       </c>
       <c r="U46" t="n">
-        <v>19.02749996185303</v>
+        <v>1129</v>
       </c>
       <c r="V46" t="n">
-        <v>18.91010268529256</v>
+        <v>1139</v>
       </c>
       <c r="W46" t="n">
-        <v>-0.1057587888602889</v>
+        <v>-17.74030052988269</v>
       </c>
       <c r="X46" t="n">
-        <v>-0.06542483415428357</v>
+        <v>-19.86038036342023</v>
       </c>
       <c r="Y46" t="n">
-        <v>-0.04033395470600531</v>
+        <v>2.120079833537545</v>
       </c>
       <c r="Z46" t="n">
-        <v>-0.05398517956514894</v>
+        <v>-1.480635292806102</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.0359897550376066</v>
+        <v>-0.03083700440528636</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.005346525497051058</v>
+        <v>-0.02222222222222225</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.07925104179429099</v>
+        <v>-0.07409829116197075</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.02535480664952461</v>
+        <v>-0.0422305033746958</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.05389623514476638</v>
+        <v>-0.03186778778727495</v>
       </c>
       <c r="AG46" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH46" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6932,22 +6932,24 @@
         <v>0</v>
       </c>
       <c r="AK46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>19.24</v>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP46" t="n">
-        <v>19.46</v>
+        <v>1163.68</v>
       </c>
     </row>
     <row r="47">
@@ -6958,12 +6960,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6972,7 +6974,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6981,15 +6983,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6998,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7007,61 +7009,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3540</v>
+        <v>18.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>3540</v>
+        <v>18.75</v>
       </c>
       <c r="R47" t="n">
-        <v>5089299</v>
+        <v>25162810</v>
       </c>
       <c r="S47" t="n">
-        <v>3425</v>
+        <v>18.70999984741211</v>
       </c>
       <c r="T47" t="n">
-        <v>3843.58193359375</v>
+        <v>18.99249992370606</v>
       </c>
       <c r="U47" t="n">
-        <v>3850.148107910156</v>
+        <v>19.02749996185303</v>
       </c>
       <c r="V47" t="n">
-        <v>3778.603556315104</v>
+        <v>18.91010268529256</v>
       </c>
       <c r="W47" t="n">
-        <v>-136.3553533146433</v>
+        <v>-0.1057587888602889</v>
       </c>
       <c r="X47" t="n">
-        <v>-56.42673552923905</v>
+        <v>-0.06542483415428357</v>
       </c>
       <c r="Y47" t="n">
-        <v>-79.9286177854042</v>
+        <v>-0.04033395470600531</v>
       </c>
       <c r="Z47" t="n">
-        <v>-111.8986719358526</v>
+        <v>-0.05398517956514892</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.03577006679394201</v>
+        <v>-0.0359897550376066</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.07812646527852174</v>
+        <v>-0.005346525497051058</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.0790313535506264</v>
+        <v>-0.07925104179429099</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.09813474643099529</v>
+        <v>-0.02535480664952461</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.01910339288036889</v>
+        <v>-0.05389623514476638</v>
       </c>
       <c r="AG47" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH47" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7079,11 +7081,13 @@
         <v>1</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>19.24</v>
+      </c>
       <c r="AP47" t="n">
-        <v>4025.61</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="48">
@@ -7094,12 +7098,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7108,7 +7112,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14.6</v>
+        <v>18.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7117,15 +7121,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5398000</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7134,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5398000</v>
+        <v>1000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7143,61 +7147,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1370</v>
+        <v>3540</v>
       </c>
       <c r="Q48" t="n">
-        <v>1370</v>
+        <v>3540</v>
       </c>
       <c r="R48" t="n">
-        <v>9606533</v>
+        <v>4889572</v>
       </c>
       <c r="S48" t="n">
-        <v>1377</v>
+        <v>3425</v>
       </c>
       <c r="T48" t="n">
-        <v>1405.75</v>
+        <v>3843.573815917969</v>
       </c>
       <c r="U48" t="n">
-        <v>1412</v>
+        <v>3850.139050292969</v>
       </c>
       <c r="V48" t="n">
-        <v>1430.583333333333</v>
+        <v>3778.5880859375</v>
       </c>
       <c r="W48" t="n">
-        <v>-19.92599234664908</v>
+        <v>-136.3515085222648</v>
       </c>
       <c r="X48" t="n">
-        <v>-20.167640543832</v>
+        <v>-56.42263399700656</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2416481971829185</v>
+        <v>-79.92887452525824</v>
       </c>
       <c r="Z48" t="n">
-        <v>-1.561773602172792</v>
+        <v>-111.898673946805</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.08361204013377932</v>
+        <v>-0.03576512947755717</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.1329113924050633</v>
+        <v>-0.07812171775920829</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.1268733268904637</v>
+        <v>-0.07902641623424156</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.1529196735575369</v>
+        <v>-0.09812999891168184</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.02604634666707317</v>
+        <v>0.01910358267744028</v>
       </c>
       <c r="AG48" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AH48" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7206,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="AK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="b">
         <v>1</v>
@@ -7217,13 +7221,9 @@
       <c r="AN48" t="b">
         <v>0</v>
       </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>1492.63</v>
+        <v>4025.58</v>
       </c>
     </row>
     <row r="49">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7289,7 +7289,7 @@
         <v>4890</v>
       </c>
       <c r="R49" t="n">
-        <v>3618480</v>
+        <v>3392081</v>
       </c>
       <c r="S49" t="n">
         <v>5026</v>
@@ -7307,13 +7307,13 @@
         <v>-160.5139129580921</v>
       </c>
       <c r="X49" t="n">
-        <v>-83.51504636773939</v>
+        <v>-83.5150463677395</v>
       </c>
       <c r="Y49" t="n">
-        <v>-76.99886659035269</v>
+        <v>-76.99886659035258</v>
       </c>
       <c r="Z49" t="n">
-        <v>-83.95358408476221</v>
+        <v>-83.95358408476207</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7427,7 +7427,7 @@
         <v>1220</v>
       </c>
       <c r="R50" t="n">
-        <v>1422506</v>
+        <v>1414053</v>
       </c>
       <c r="S50" t="n">
         <v>1251</v>
@@ -7442,13 +7442,13 @@
         <v>1382.257293701172</v>
       </c>
       <c r="W50" t="n">
-        <v>-49.78210545852244</v>
+        <v>-49.78210545852198</v>
       </c>
       <c r="X50" t="n">
-        <v>-38.73110277324523</v>
+        <v>-38.73110277324496</v>
       </c>
       <c r="Y50" t="n">
-        <v>-11.0510026852772</v>
+        <v>-11.05100268527702</v>
       </c>
       <c r="Z50" t="n">
         <v>-11.58266004238281</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4.8</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7533,15 +7533,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1364000</v>
+        <v>1159000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7550,13 +7550,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1516000</v>
+        <v>1364000</v>
       </c>
       <c r="N51" t="n">
-        <v>-152000</v>
+        <v>-205000</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.1002638522427441</v>
+        <v>-0.1502932551319648</v>
       </c>
       <c r="P51" t="n">
         <v>902</v>
@@ -7565,7 +7565,7 @@
         <v>902</v>
       </c>
       <c r="R51" t="n">
-        <v>1069844</v>
+        <v>1006864</v>
       </c>
       <c r="S51" t="n">
         <v>887.2</v>
@@ -7586,10 +7586,10 @@
         <v>-27.06376278695161</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.02197627463449</v>
+        <v>2.021976274634493</v>
       </c>
       <c r="Z51" t="n">
-        <v>-0.7750007364018998</v>
+        <v>-0.7750007364018963</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
